--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488236_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488236_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.8377</v>
+        <v>5.2594</v>
       </c>
       <c r="E2" t="n">
-        <v>3.7594</v>
+        <v>3.5751</v>
       </c>
       <c r="F2" t="n">
-        <v>2.0783</v>
+        <v>1.6843</v>
       </c>
       <c r="G2" t="n">
         <v>4.5458</v>
@@ -610,13 +610,13 @@
         <v>1.6676</v>
       </c>
       <c r="S2" t="n">
-        <v>1.7917</v>
+        <v>1.2134</v>
       </c>
       <c r="T2" t="n">
-        <v>0.4514</v>
+        <v>0.2671</v>
       </c>
       <c r="U2" t="n">
-        <v>1.3402</v>
+        <v>0.9463</v>
       </c>
       <c r="V2" t="n">
         <v>-0.3144</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.3458</v>
+        <v>5.2589</v>
       </c>
       <c r="E3" t="n">
-        <v>1.9633</v>
+        <v>2.6056</v>
       </c>
       <c r="F3" t="n">
-        <v>2.3824</v>
+        <v>2.6533</v>
       </c>
       <c r="G3" t="n">
         <v>4.9315</v>
@@ -688,13 +688,13 @@
         <v>1.4823</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.5482</v>
+        <v>0.365</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6901</v>
+        <v>-0.0479</v>
       </c>
       <c r="U3" t="n">
-        <v>0.142</v>
+        <v>0.4128</v>
       </c>
       <c r="V3" t="n">
         <v>1.2594</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. ESCAMILLA DE SANTOS</t>
+          <t>J. REMESAL LEÓN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3034</v>
+        <v>1.2662</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.4783</v>
+        <v>1.2662</v>
       </c>
       <c r="F4" t="n">
-        <v>1.7817</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>1.3083</v>
+        <v>1.2662</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.3168</v>
+        <v>0.6441</v>
       </c>
       <c r="I4" t="n">
-        <v>1.6252</v>
+        <v>0.6221</v>
       </c>
       <c r="J4" t="n">
-        <v>1.3194</v>
+        <v>1.2662</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5623</v>
+        <v>0.6441</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7572</v>
+        <v>0.6221</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.0111</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.8791</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0.868</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.8529</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.7793</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9264</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0.9035</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2773</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.1808</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>0.9444</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.2589</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.3144</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. REMESAL LEÓN</t>
+          <t>D. ESCAMILLA DE SANTOS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2662</v>
+        <v>0.7005</v>
       </c>
       <c r="E5" t="n">
-        <v>1.2662</v>
+        <v>-0.6627</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1.3632</v>
       </c>
       <c r="G5" t="n">
-        <v>1.2662</v>
+        <v>1.3083</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6441</v>
+        <v>-0.3168</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6221</v>
+        <v>1.6252</v>
       </c>
       <c r="J5" t="n">
-        <v>1.2662</v>
+        <v>1.3194</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6441</v>
+        <v>0.5623</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6221</v>
+        <v>0.7572</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>-0.0111</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>-0.8791</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>0.868</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>-1.8529</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-2.7793</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>0.9264</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>0.3006</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>-0.4616</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>0.7623</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.9444</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.2589</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4887</v>
+        <v>0.6659</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8447</v>
+        <v>0.9973</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.356</v>
+        <v>-0.3314</v>
       </c>
       <c r="G6" t="n">
         <v>0.0594</v>
@@ -922,13 +922,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1266</v>
+        <v>0.0507</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.143</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0164</v>
+        <v>0.041</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2494</v>
+        <v>0.0292</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.05</v>
+        <v>-1.387</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8007</v>
+        <v>1.4162</v>
       </c>
       <c r="G7" t="n">
         <v>-1.7144</v>
@@ -1000,13 +1000,13 @@
         <v>1.4823</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2972</v>
+        <v>0.5758</v>
       </c>
       <c r="T7" t="n">
-        <v>0.485</v>
+        <v>0.148</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1878</v>
+        <v>0.4278</v>
       </c>
       <c r="V7" t="n">
         <v>-0.3144</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.3844</v>
+        <v>-0.5742</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2688</v>
+        <v>0.0297</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.6532</v>
+        <v>-0.6039</v>
       </c>
       <c r="G8" t="n">
         <v>-1.4291</v>
@@ -1078,13 +1078,13 @@
         <v>0.7411</v>
       </c>
       <c r="S8" t="n">
-        <v>0.6185</v>
+        <v>0.4287</v>
       </c>
       <c r="T8" t="n">
-        <v>0.5857</v>
+        <v>0.3466</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0328</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="V8" t="n">
         <v>-0.315</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.5142</v>
+        <v>-1.239</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.5034</v>
+        <v>-1.2529</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.0107</v>
+        <v>0.0139</v>
       </c>
       <c r="G9" t="n">
         <v>-1.8887</v>
@@ -1156,13 +1156,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1813</v>
+        <v>0.0939</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1977</v>
+        <v>0.0529</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0164</v>
+        <v>0.041</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.8016</v>
+        <v>-1.4957</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0035</v>
+        <v>0.2108</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.8051</v>
+        <v>-1.7066</v>
       </c>
       <c r="G10" t="n">
         <v>-0.9101</v>
@@ -1234,13 +1234,13 @@
         <v>0.1853</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4479</v>
+        <v>-0.1421</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.383</v>
+        <v>-0.1756</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0649</v>
+        <v>0.0336</v>
       </c>
       <c r="V10" t="n">
         <v>-0.6289</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.4154</v>
+        <v>-1.9077</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.5755</v>
+        <v>-1.2155</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.8399</v>
+        <v>-0.6922</v>
       </c>
       <c r="G11" t="n">
         <v>-1.5415</v>
@@ -1312,13 +1312,13 @@
         <v>0.7411</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6887</v>
+        <v>-0.1809</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3954</v>
+        <v>-0.0354</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2932</v>
+        <v>-0.1455</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.0012</v>
+        <v>-3.6188</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.5685</v>
+        <v>-3.8167</v>
       </c>
       <c r="F12" t="n">
-        <v>0.5673</v>
+        <v>0.1979</v>
       </c>
       <c r="G12" t="n">
         <v>-1.5761</v>
@@ -1390,13 +1390,13 @@
         <v>1.6676</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2076</v>
+        <v>0.59</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.0184</v>
+        <v>-0.2667</v>
       </c>
       <c r="U12" t="n">
-        <v>1.2261</v>
+        <v>0.8568</v>
       </c>
       <c r="V12" t="n">
         <v>1.2583</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.3776</v>
+        <v>-6.7523</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.6575</v>
+        <v>-5.983</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.7201</v>
+        <v>-0.7693</v>
       </c>
       <c r="G13" t="n">
         <v>-7.1134</v>
@@ -1468,13 +1468,13 @@
         <v>1.1117</v>
       </c>
       <c r="S13" t="n">
-        <v>0.8476</v>
+        <v>0.4729</v>
       </c>
       <c r="T13" t="n">
-        <v>0.725</v>
+        <v>0.3995</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1226</v>
+        <v>0.07340000000000001</v>
       </c>
       <c r="V13" t="n">
         <v>0.6294</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-3.502000000000002</v>
+        <v>-2.4076</v>
       </c>
       <c r="E14" t="n">
-        <v>-6.7273</v>
+        <v>-5.633099999999999</v>
       </c>
       <c r="F14" t="n">
         <v>3.2254</v>
@@ -1546,13 +1546,13 @@
         <v>11.1172</v>
       </c>
       <c r="S14" t="n">
-        <v>2.6734</v>
+        <v>3.768</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.8578</v>
+        <v>0.2365</v>
       </c>
       <c r="U14" t="n">
-        <v>3.5314</v>
+        <v>3.5316</v>
       </c>
       <c r="V14" t="n">
         <v>2.5188</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. CASTILLO ORTEGA</t>
+          <t>F. RUESGA MORALES</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.0081</v>
+        <v>3.6649</v>
       </c>
       <c r="E15" t="n">
-        <v>2.5912</v>
+        <v>1.3658</v>
       </c>
       <c r="F15" t="n">
-        <v>1.4169</v>
+        <v>2.2992</v>
       </c>
       <c r="G15" t="n">
-        <v>1.511</v>
+        <v>4.9766</v>
       </c>
       <c r="H15" t="n">
-        <v>1.0869</v>
+        <v>2.0949</v>
       </c>
       <c r="I15" t="n">
-        <v>0.4241</v>
+        <v>2.8816</v>
       </c>
       <c r="J15" t="n">
-        <v>2.7345</v>
+        <v>4.2277</v>
       </c>
       <c r="K15" t="n">
-        <v>2.6101</v>
+        <v>2.8899</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1244</v>
+        <v>1.3378</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.2235</v>
+        <v>0.7489</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.5233</v>
+        <v>-0.795</v>
       </c>
       <c r="O15" t="n">
-        <v>0.2997</v>
+        <v>1.5439</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.1117</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="Q15" t="n">
-        <v>-3.7057</v>
+        <v>-1.8529</v>
       </c>
       <c r="R15" t="n">
-        <v>2.594</v>
+        <v>2.4087</v>
       </c>
       <c r="S15" t="n">
-        <v>1.4067</v>
+        <v>-0.2925</v>
       </c>
       <c r="T15" t="n">
-        <v>1.0459</v>
+        <v>-0.6929</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3608</v>
+        <v>0.4004</v>
       </c>
       <c r="V15" t="n">
-        <v>2.2022</v>
+        <v>-1.5749</v>
       </c>
       <c r="W15" t="n">
-        <v>2.5166</v>
+        <v>-0.3161</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.3144</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>F. RUESGA MORALES</t>
+          <t>A. CASTILLO ORTEGA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.806</v>
+        <v>2.8903</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8761</v>
+        <v>1.3182</v>
       </c>
       <c r="F16" t="n">
-        <v>1.9298</v>
+        <v>1.5721</v>
       </c>
       <c r="G16" t="n">
-        <v>4.9766</v>
+        <v>1.511</v>
       </c>
       <c r="H16" t="n">
-        <v>2.0949</v>
+        <v>1.0869</v>
       </c>
       <c r="I16" t="n">
-        <v>2.8816</v>
+        <v>0.4241</v>
       </c>
       <c r="J16" t="n">
-        <v>4.2277</v>
+        <v>2.7345</v>
       </c>
       <c r="K16" t="n">
-        <v>2.8899</v>
+        <v>2.6101</v>
       </c>
       <c r="L16" t="n">
-        <v>1.3378</v>
+        <v>0.1244</v>
       </c>
       <c r="M16" t="n">
-        <v>0.7489</v>
+        <v>-1.2235</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.795</v>
+        <v>-1.5233</v>
       </c>
       <c r="O16" t="n">
-        <v>1.5439</v>
+        <v>0.2997</v>
       </c>
       <c r="P16" t="n">
-        <v>0.5558999999999999</v>
+        <v>-1.1117</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.8529</v>
+        <v>-3.7057</v>
       </c>
       <c r="R16" t="n">
-        <v>2.4087</v>
+        <v>2.594</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.1515</v>
+        <v>0.2888</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.1826</v>
+        <v>-0.2272</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0311</v>
+        <v>0.516</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.5749</v>
+        <v>2.2022</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.3161</v>
+        <v>2.5166</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.2589</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.4292</v>
+        <v>2.6812</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.4141</v>
+        <v>-0.1203</v>
       </c>
       <c r="F17" t="n">
-        <v>2.8433</v>
+        <v>2.8015</v>
       </c>
       <c r="G17" t="n">
         <v>1.1887</v>
@@ -1780,13 +1780,13 @@
         <v>1.297</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0565</v>
+        <v>0.1955</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2736</v>
+        <v>0.0202</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2171</v>
+        <v>0.1753</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.7151</v>
+        <v>1.1229</v>
       </c>
       <c r="E18" t="n">
-        <v>1.6045</v>
+        <v>1.8004</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.8894</v>
+        <v>-0.6775</v>
       </c>
       <c r="G18" t="n">
         <v>0.4547</v>
@@ -1858,13 +1858,13 @@
         <v>0.7411</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.7951</v>
+        <v>-0.3874</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4377</v>
+        <v>-0.2419</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3574</v>
+        <v>-0.1455</v>
       </c>
       <c r="V18" t="n">
         <v>0.3144</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. LÓPEZ RUIZ</t>
+          <t>R. VARELA SANCHEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3221</v>
+        <v>0.8426</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3221</v>
+        <v>-0.4899</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>1.3324</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3221</v>
+        <v>0.9381</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3221</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>0.0062</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3221</v>
+        <v>0.5373</v>
       </c>
       <c r="K19" t="n">
-        <v>0.3221</v>
+        <v>0.4851</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>0.0522</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>0.4009</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>0.4469</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>-0.046</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>0.3706</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.297</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>-0.1517</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>-0.1007</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>-0.051</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-0.3144</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R. VARELA SANCHEZ</t>
+          <t>E. NGOM</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2218</v>
+        <v>0.5464</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.8816000000000001</v>
+        <v>-2.8621</v>
       </c>
       <c r="F20" t="n">
-        <v>1.1034</v>
+        <v>3.4085</v>
       </c>
       <c r="G20" t="n">
-        <v>0.9381</v>
+        <v>-0.5058</v>
       </c>
       <c r="H20" t="n">
-        <v>0.9320000000000001</v>
+        <v>-0.1555</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0062</v>
+        <v>-0.3502</v>
       </c>
       <c r="J20" t="n">
-        <v>0.5373</v>
+        <v>-1.4749</v>
       </c>
       <c r="K20" t="n">
-        <v>0.4851</v>
+        <v>-0.2107</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0522</v>
+        <v>-1.2643</v>
       </c>
       <c r="M20" t="n">
-        <v>0.4009</v>
+        <v>0.9692</v>
       </c>
       <c r="N20" t="n">
-        <v>0.4469</v>
+        <v>0.0552</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.046</v>
+        <v>0.914</v>
       </c>
       <c r="P20" t="n">
-        <v>0.3706</v>
+        <v>0.7411</v>
       </c>
       <c r="Q20" t="n">
         <v>-0.9264</v>
       </c>
       <c r="R20" t="n">
-        <v>1.297</v>
+        <v>1.6676</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7725</v>
+        <v>-0.319</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4924</v>
+        <v>-0.4607</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2801</v>
+        <v>0.1418</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.3144</v>
+        <v>0.63</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.3144</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>E. NGOM</t>
+          <t>J. LÓPEZ RUIZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0968</v>
+        <v>0.3221</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.0579</v>
+        <v>0.3221</v>
       </c>
       <c r="F21" t="n">
-        <v>3.1548</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.5058</v>
+        <v>0.3221</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.1555</v>
+        <v>0.3221</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3502</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.4749</v>
+        <v>0.3221</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.2107</v>
+        <v>0.3221</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.2643</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.9692</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>0.0552</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>0.914</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>0.7411</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.6676</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7685</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6566</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1119</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>0.63</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0.63</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.2376</v>
+        <v>-0.7147</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.18</v>
+        <v>-1.8862</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9424</v>
+        <v>1.1715</v>
       </c>
       <c r="G22" t="n">
         <v>-3.3666</v>
@@ -2170,13 +2170,13 @@
         <v>1.8529</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.9826</v>
+        <v>-0.4598</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.1279</v>
+        <v>-0.8341</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1452</v>
+        <v>0.3743</v>
       </c>
       <c r="V22" t="n">
         <v>1.2589</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.525</v>
+        <v>-1.6069</v>
       </c>
       <c r="E23" t="n">
-        <v>1.3827</v>
+        <v>1.0889</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.9077</v>
+        <v>-2.6958</v>
       </c>
       <c r="G23" t="n">
         <v>0.6903</v>
@@ -2248,13 +2248,13 @@
         <v>0.7411</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1423</v>
+        <v>-0.2241</v>
       </c>
       <c r="T23" t="n">
-        <v>0.2151</v>
+        <v>-0.0786</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3574</v>
+        <v>-0.1455</v>
       </c>
       <c r="V23" t="n">
         <v>-1.8877</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.6861</v>
+        <v>-2.4483</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.1226</v>
+        <v>-3.3184</v>
       </c>
       <c r="F24" t="n">
-        <v>1.4365</v>
+        <v>0.8702</v>
       </c>
       <c r="G24" t="n">
         <v>-2.0504</v>
@@ -2326,13 +2326,13 @@
         <v>1.297</v>
       </c>
       <c r="S24" t="n">
-        <v>1.2515</v>
+        <v>0.4893</v>
       </c>
       <c r="T24" t="n">
-        <v>0.0721</v>
+        <v>-0.1237</v>
       </c>
       <c r="U24" t="n">
-        <v>1.1793</v>
+        <v>0.613</v>
       </c>
       <c r="V24" t="n">
         <v>-1.2578</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.6486</v>
+        <v>-2.4929</v>
       </c>
       <c r="E25" t="n">
-        <v>1.2279</v>
+        <v>1.13</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.8766</v>
+        <v>-3.6229</v>
       </c>
       <c r="G25" t="n">
         <v>-0.0965</v>
@@ -2404,13 +2404,13 @@
         <v>1.8529</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.6627999999999999</v>
+        <v>-0.507</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.6939</v>
+        <v>-0.7917999999999999</v>
       </c>
       <c r="U25" t="n">
-        <v>0.0311</v>
+        <v>0.2848</v>
       </c>
       <c r="V25" t="n">
         <v>-1.8894</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>3.501799999999999</v>
+        <v>4.807599999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.651699999999999</v>
+        <v>-1.6515</v>
       </c>
       <c r="F26" t="n">
-        <v>5.153400000000001</v>
+        <v>6.459199999999999</v>
       </c>
       <c r="G26" t="n">
         <v>4.062200000000001</v>
@@ -2470,7 +2470,7 @@
         <v>-6.0785</v>
       </c>
       <c r="O26" t="n">
-        <v>2.804400000000001</v>
+        <v>2.8044</v>
       </c>
       <c r="P26" t="n">
         <v>4.632199999999999</v>
@@ -2482,13 +2482,13 @@
         <v>15.7493</v>
       </c>
       <c r="S26" t="n">
-        <v>-2.6736</v>
+        <v>-1.3679</v>
       </c>
       <c r="T26" t="n">
-        <v>-3.5316</v>
+        <v>-3.5314</v>
       </c>
       <c r="U26" t="n">
-        <v>0.8578</v>
+        <v>2.1636</v>
       </c>
       <c r="V26" t="n">
         <v>-2.5187</v>
